--- a/data/Inside_Airbnb_Data_Dictionary.xlsx
+++ b/data/Inside_Airbnb_Data_Dictionary.xlsx
@@ -1,303 +1,252 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="hidden" name="listings.csv detail v4.7" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="listings.csv detail v4.3" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="listings.csv detail v4" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="listings.csv detail v3" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="listings.csv summary v2" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="listings.csv summary v1" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="reviews.csv v1" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="calendar.csv v2" sheetId="8" r:id="rId12"/>
-    <sheet state="visible" name="calendar.csv v1" sheetId="9" r:id="rId13"/>
+    <sheet name="listings.csv detail v4.7" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="listings.csv detail v4.3" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="listings.csv detail v4" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="listings.csv detail v3" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="listings.csv summary v2" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="listings.csv summary v1" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="reviews.csv v1" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="calendar.csv v2" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="calendar.csv v1" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="231">
   <si>
-    <t>Data Dictionary for listings.csv detailed file</t>
-  </si>
-  <si>
-    <t>File Name</t>
-  </si>
-  <si>
-    <t>listings.csv</t>
-  </si>
-  <si>
-    <t>Version</t>
-  </si>
-  <si>
-    <t>Date Introduced</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Calculated</t>
-  </si>
-  <si>
-    <t>Reference</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>Airbnb's unique identifier for the listing</t>
-  </si>
-  <si>
-    <t>listing_url</t>
-  </si>
-  <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>scrape_id</t>
-  </si>
-  <si>
-    <t>bigint</t>
-  </si>
-  <si>
-    <t>Inside Airbnb "Scrape" this was part of</t>
-  </si>
-  <si>
-    <t>last_scraped</t>
-  </si>
-  <si>
-    <t>datetime</t>
-  </si>
-  <si>
-    <t>UTC. The date and time this listing was "scraped".</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>Name of the listing</t>
-  </si>
-  <si>
-    <t>summary</t>
-  </si>
-  <si>
-    <t>Summary description of the listing</t>
-  </si>
-  <si>
-    <t>space</t>
-  </si>
-  <si>
-    <t>Description of the space for rent</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>Detailed description of the listing</t>
-  </si>
-  <si>
-    <t>source</t>
-  </si>
-  <si>
-    <t>experiences_offered</t>
-  </si>
-  <si>
-    <t>One of "neighbourhood search" or "previous scrape". "neighbourhood search" means that the listing was found by searching the city, while "previous scrape" means that the listing was seen in another scrape performed in the last 65 days, and the listing was confirmed to be still available on the Airbnb site.</t>
-  </si>
-  <si>
-    <t>Description of the experiences offered</t>
-  </si>
-  <si>
-    <t>neighborhood_overview</t>
-  </si>
-  <si>
-    <t>Host's description of the neighbourhood</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>Notes for the listing. In some cities, Airbnb instructs the host to write the legal Permit #, in liue of using the license_number field</t>
-  </si>
-  <si>
-    <t>transit</t>
-  </si>
-  <si>
-    <t>Notes for the listing</t>
-  </si>
-  <si>
-    <t>access</t>
-  </si>
-  <si>
-    <t>Access notes</t>
-  </si>
-  <si>
-    <t>interaction</t>
-  </si>
-  <si>
-    <t>house_rules</t>
-  </si>
-  <si>
-    <t>thumbnail_url</t>
-  </si>
-  <si>
-    <t>URL to the Airbnb hosted thumbnail image for the listing</t>
-  </si>
-  <si>
-    <t>picture_url</t>
-  </si>
-  <si>
-    <t>medium_url</t>
-  </si>
-  <si>
-    <t>URL to the Airbnb hosted regular sized image for the listing</t>
-  </si>
-  <si>
-    <t>host_id</t>
-  </si>
-  <si>
-    <t>Airbnb's unique identifier for the host/user</t>
-  </si>
-  <si>
-    <t>host_url</t>
-  </si>
-  <si>
-    <t>The Airbnb page for the host</t>
-  </si>
-  <si>
-    <t>host_name</t>
-  </si>
-  <si>
-    <t>Name of the host. Usually just the first name(s).</t>
-  </si>
-  <si>
-    <t>host_since</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>The date the host/user was created. For hosts that are Airbnb guests this could be the date they registered as a guest.</t>
-  </si>
-  <si>
-    <t>host_location</t>
-  </si>
-  <si>
-    <t>The host's self reported location</t>
-  </si>
-  <si>
-    <t>host_about</t>
-  </si>
-  <si>
-    <t>Description about the host</t>
-  </si>
-  <si>
-    <t>host_response_time</t>
-  </si>
-  <si>
-    <t>host_response_rate</t>
-  </si>
-  <si>
-    <t>URL to the Airbnb hosted medium sized image for the listing</t>
-  </si>
-  <si>
-    <t>host_acceptance_rate</t>
-  </si>
-  <si>
-    <t>That rate at which a host accepts booking requests.</t>
-  </si>
-  <si>
-    <t>host_is_superhost</t>
-  </si>
-  <si>
-    <t>boolean [t=true; f=false]</t>
-  </si>
-  <si>
-    <t>xl_picture_url</t>
-  </si>
-  <si>
-    <t>host_thumbnail_url</t>
-  </si>
-  <si>
-    <t>URL to the Airbnb hosted XL sized image for the listing</t>
-  </si>
-  <si>
-    <t>host_picture_url</t>
-  </si>
-  <si>
-    <t>host_neighbourhood</t>
-  </si>
-  <si>
-    <t>host_listings_count</t>
-  </si>
-  <si>
-    <t>The number of listings the host has (per Airbnb unknown calculations)</t>
-  </si>
-  <si>
-    <t>host_total_listings_count</t>
-  </si>
-  <si>
-    <t>host_verifications</t>
-  </si>
-  <si>
-    <t>host_has_profile_pic</t>
-  </si>
-  <si>
-    <t>host_identity_verified</t>
-  </si>
-  <si>
-    <t>neighbourhood</t>
-  </si>
-  <si>
-    <t>neighbourhood_cleansed</t>
-  </si>
-  <si>
-    <t>The neighbourhood as geocoded using the latitude and longitude against neighborhoods as defined by open or public digital shapefiles.</t>
-  </si>
-  <si>
-    <t>neighbourhood_group_cleansed</t>
-  </si>
-  <si>
-    <t>The neighbourhood group as geocoded using the latitude and longitude against neighborhoods as defined by open or public digital shapefiles.</t>
-  </si>
-  <si>
-    <t>latitude</t>
-  </si>
-  <si>
-    <t>numeric</t>
-  </si>
-  <si>
-    <t>Uses the World Geodetic System (WGS84) projection for latitude and longitude.</t>
-  </si>
-  <si>
-    <t>longitude</t>
-  </si>
-  <si>
-    <t>property_type</t>
-  </si>
-  <si>
-    <t>Self selected property type. Hotels and Bed and Breakfasts are described as such by their hosts in this field</t>
-  </si>
-  <si>
-    <t>room_type</t>
-  </si>
-  <si>
-    <t>[Entire home/apt|Private room|Shared room|Hotel]
+    <t xml:space="preserve">Data Dictionary for listings.csv detailed file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">listings.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date Introduced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airbnb's unique identifier for the listing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">listing_url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scrape_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bigint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inside Airbnb "Scrape" this was part of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">last_scraped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">datetime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UTC. The date and time this listing was "scraped".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One of "neighbourhood search" or "previous scrape". "neighbourhood search" means that the listing was found by searching the city, while "previous scrape" means that the listing was seen in another scrape performed in the last 65 days, and the listing was confirmed to be still available on the Airbnb site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name of the listing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detailed description of the listing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neighborhood_overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Host's description of the neighbourhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">picture_url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL to the Airbnb hosted regular sized image for the listing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airbnb's unique identifier for the host/user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Airbnb page for the host</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name of the host. Usually just the first name(s).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_since</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The date the host/user was created. For hosts that are Airbnb guests this could be the date they registered as a guest.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The host's self reported location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_about</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description about the host</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_response_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_response_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_acceptance_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That rate at which a host accepts booking requests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_is_superhost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean [t=true; f=false]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_thumbnail_url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_picture_url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_neighbourhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_listings_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of listings the host has (per Airbnb unknown calculations)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_total_listings_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_verifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_has_profile_pic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">host_identity_verified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neighbourhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neighbourhood_cleansed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The neighbourhood as geocoded using the latitude and longitude against neighborhoods as defined by open or public digital shapefiles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neighbourhood_group_cleansed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The neighbourhood group as geocoded using the latitude and longitude against neighborhoods as defined by open or public digital shapefiles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">latitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">numeric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uses the World Geodetic System (WGS84) projection for latitude and longitude.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">longitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">property_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self selected property type. Hotels and Bed and Breakfasts are described as such by their hosts in this field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">room_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Entire home/apt|Private room|Shared room|Hotel]
 All homes are grouped into the following three room types:
 Entire place
 Private room
@@ -310,311 +259,225 @@
 Shared rooms are for when you don't mind sharing a space with others. When you book a shared room, you'll be sleeping in a space that is shared with others and share the entire space with other people. Shared rooms are popular among flexible travelers looking for new friends and budget-friendly stays.</t>
   </si>
   <si>
-    <t>The number of listings the host has (per Airbnb calculations)</t>
-  </si>
-  <si>
-    <t>https://www.airbnb.com/help/article/5/what-does-the-room-type-of-a-listing-mean</t>
-  </si>
-  <si>
-    <t>The number of listings the host has</t>
-  </si>
-  <si>
-    <t>street</t>
-  </si>
-  <si>
-    <t>city</t>
-  </si>
-  <si>
-    <t>state</t>
-  </si>
-  <si>
-    <t>zipcode</t>
-  </si>
-  <si>
-    <t>market</t>
-  </si>
-  <si>
-    <t>smart_location</t>
-  </si>
-  <si>
-    <t>country_code</t>
-  </si>
-  <si>
-    <t>country</t>
-  </si>
-  <si>
-    <t>is_location_exact</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>[t=true; f=false]
-Possibly related to the host's choice for displaying the listing's location. See references.</t>
-  </si>
-  <si>
-    <t>https://www.airbnb.com/help/article/2141/how-will-my-listings-location-be-shown-on-the-map
-https://www.airbnb.com/help/article/478/how-do-i-edit-my-listings-address-or-map-location</t>
-  </si>
-  <si>
-    <t>accommodates</t>
-  </si>
-  <si>
-    <t>The maximum capacity of the listing</t>
-  </si>
-  <si>
-    <t>bathrooms</t>
-  </si>
-  <si>
-    <t>The number of bathrooms in the listing</t>
-  </si>
-  <si>
-    <t>bathrooms_text</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>The number of bathrooms in the listing. 
+    <t xml:space="preserve">https://www.airbnb.com/help/article/5/what-does-the-room-type-of-a-listing-mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accommodates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The maximum capacity of the listing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bathrooms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of bathrooms in the listing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bathrooms_text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of bathrooms in the listing. 
 On the Airbnb web-site, the bathrooms field has evolved from a number to a textual description. For older scrapes, bathrooms is used.</t>
   </si>
   <si>
-    <t>bedrooms</t>
-  </si>
-  <si>
-    <t>The number of bedrooms</t>
-  </si>
-  <si>
-    <t>beds</t>
-  </si>
-  <si>
-    <t>The number of bed(s)</t>
-  </si>
-  <si>
-    <t>amenities</t>
-  </si>
-  <si>
-    <t>json</t>
-  </si>
-  <si>
-    <t>price</t>
-  </si>
-  <si>
-    <t>currency</t>
-  </si>
-  <si>
-    <t>daily price in local currency.
+    <t xml:space="preserve">bedrooms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of bedrooms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of bed(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amenities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daily price in local currency.
 NOTE: the $ sign is a technical artifact of the export, please ignore it</t>
   </si>
   <si>
-    <t>minimum_nights</t>
-  </si>
-  <si>
-    <t>minimum number of night stay for the listing (calendar rules may be different)</t>
-  </si>
-  <si>
-    <t>maximum_nights</t>
-  </si>
-  <si>
-    <t>maximum number of night stay for the listing (calendar rules may be different)</t>
-  </si>
-  <si>
-    <t>minimum_minimum_nights</t>
-  </si>
-  <si>
-    <t>the smallest minimum_night value from the calender (looking 365 nights in the future)</t>
-  </si>
-  <si>
-    <t>maximum_minimum_nights</t>
-  </si>
-  <si>
-    <t>the largest minimum_night value from the calender (looking 365 nights in the future)</t>
-  </si>
-  <si>
-    <t>minimum_maximum_nights</t>
-  </si>
-  <si>
-    <t>the smallest maximum_night value from the calender (looking 365 nights in the future)</t>
-  </si>
-  <si>
-    <t>maximum_maximum_nights</t>
-  </si>
-  <si>
-    <t>the largest maximum_night value from the calender (looking 365 nights in the future)</t>
-  </si>
-  <si>
-    <t>minimum_nights_avg_ntm</t>
-  </si>
-  <si>
-    <t>the average minimum_night value from the calender (looking 365 nights in the future)</t>
-  </si>
-  <si>
-    <t>maximum_nights_avg_ntm</t>
-  </si>
-  <si>
-    <t>the average maximum_night value from the calender (looking 365 nights in the future)</t>
-  </si>
-  <si>
-    <t>calendar_updated</t>
-  </si>
-  <si>
-    <t>bed_type</t>
-  </si>
-  <si>
-    <t>The type of bed(s)</t>
-  </si>
-  <si>
-    <t>has_availability</t>
-  </si>
-  <si>
-    <t>[t=true; f=false]</t>
-  </si>
-  <si>
-    <t>availability_30</t>
-  </si>
-  <si>
-    <t>square_feet</t>
-  </si>
-  <si>
-    <t>avaliability_x. The availability of the listing x days in the future as determined by the calendar. Note a listing may not be available because it has been booked by a guest or blocked by the host.</t>
-  </si>
-  <si>
-    <t>availability_60</t>
-  </si>
-  <si>
-    <t>availability_90</t>
-  </si>
-  <si>
-    <t>daily price in local currency</t>
-  </si>
-  <si>
-    <t>weekly_price</t>
-  </si>
-  <si>
-    <t>weekly price in local currency</t>
-  </si>
-  <si>
-    <t>monthly_price</t>
-  </si>
-  <si>
-    <t>availability_365</t>
-  </si>
-  <si>
-    <t>monthly price in local currency</t>
-  </si>
-  <si>
-    <t>security_deposit</t>
-  </si>
-  <si>
-    <t>calendar_last_scraped</t>
-  </si>
-  <si>
-    <t>cleaning_fee</t>
-  </si>
-  <si>
-    <t>number_of_reviews</t>
-  </si>
-  <si>
-    <t>The number of reviews the listing has</t>
-  </si>
-  <si>
-    <t>guests_included</t>
-  </si>
-  <si>
-    <t>number</t>
-  </si>
-  <si>
-    <t>number_of_reviews_ltm</t>
-  </si>
-  <si>
-    <t>number of guests included in the price</t>
-  </si>
-  <si>
-    <t>extra_people</t>
-  </si>
-  <si>
-    <t>The number of reviews the listing has (in the last 12 months)</t>
-  </si>
-  <si>
-    <t>number_of_reviews_l30d</t>
-  </si>
-  <si>
-    <t>amount in local currency for additional guests</t>
-  </si>
-  <si>
-    <t>The number of reviews the listing has (in the last 30 days)</t>
-  </si>
-  <si>
-    <t>first_review</t>
-  </si>
-  <si>
-    <t>The date of the first/oldest review</t>
-  </si>
-  <si>
-    <t>last_review</t>
-  </si>
-  <si>
-    <t>The date of the last/newest review</t>
-  </si>
-  <si>
-    <t>review_scores_rating</t>
-  </si>
-  <si>
-    <t>review_scores_accuracy</t>
-  </si>
-  <si>
-    <t>review_scores_cleanliness</t>
-  </si>
-  <si>
-    <t>review_scores_checkin</t>
-  </si>
-  <si>
-    <t>review_scores_communication</t>
-  </si>
-  <si>
-    <t>review_scores_location</t>
-  </si>
-  <si>
-    <t>review_scores_value</t>
-  </si>
-  <si>
-    <t>license</t>
-  </si>
-  <si>
-    <t>The licence/permit/registration number</t>
-  </si>
-  <si>
-    <t>instant_bookable</t>
-  </si>
-  <si>
-    <t>[t=true; f=false]. Whether the guest can automatically book the listing without the host requiring to accept their booking request. An indicator of a commercial listing.</t>
-  </si>
-  <si>
-    <t>calculated_host_listings_count</t>
-  </si>
-  <si>
-    <t>The number of listings the host has in the current scrape, in the city/region geography.</t>
-  </si>
-  <si>
-    <t>calculated_host_listings_count_entire_homes</t>
-  </si>
-  <si>
-    <t>The number of Entire home/apt listings the host has in the current scrape, in the city/region geography</t>
-  </si>
-  <si>
-    <t>calculated_host_listings_count_private_rooms</t>
-  </si>
-  <si>
-    <t>The number of Private room listings the host has in the current scrape, in the city/region geography</t>
-  </si>
-  <si>
-    <t>calculated_host_listings_count_shared_rooms</t>
-  </si>
-  <si>
-    <t>The number of Shared room listings the host has in the current scrape, in the city/region geography</t>
-  </si>
-  <si>
-    <t>reviews_per_month</t>
+    <t xml:space="preserve">minimum_nights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minimum number of night stay for the listing (calendar rules may be different)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maximum_nights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maximum number of night stay for the listing (calendar rules may be different)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minimum_minimum_nights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the smallest minimum_night value from the calender (looking 365 nights in the future)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maximum_minimum_nights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the largest minimum_night value from the calender (looking 365 nights in the future)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minimum_maximum_nights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the smallest maximum_night value from the calender (looking 365 nights in the future)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maximum_maximum_nights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the largest maximum_night value from the calender (looking 365 nights in the future)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minimum_nights_avg_ntm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the average minimum_night value from the calender (looking 365 nights in the future)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maximum_nights_avg_ntm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the average maximum_night value from the calender (looking 365 nights in the future)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calendar_updated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has_availability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[t=true; f=false]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">availability_30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avaliability_x. The availability of the listing x days in the future as determined by the calendar. Note a listing may not be available because it has been booked by a guest or blocked by the host.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">availability_60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">availability_90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">availability_365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calendar_last_scraped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">number_of_reviews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of reviews the listing has</t>
+  </si>
+  <si>
+    <t xml:space="preserve">number_of_reviews_ltm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of reviews the listing has (in the last 12 months)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">number_of_reviews_l30d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of reviews the listing has (in the last 30 days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">first_review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The date of the first/oldest review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">last_review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The date of the last/newest review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">review_scores_rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">review_scores_accuracy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">review_scores_cleanliness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">review_scores_checkin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">review_scores_communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">review_scores_location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">review_scores_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">license</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The licence/permit/registration number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant_bookable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[t=true; f=false]. Whether the guest can automatically book the listing without the host requiring to accept their booking request. An indicator of a commercial listing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calculated_host_listings_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of listings the host has in the current scrape, in the city/region geography.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calculated_host_listings_count_entire_homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of Entire home/apt listings the host has in the current scrape, in the city/region geography</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calculated_host_listings_count_private_rooms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of Private room listings the host has in the current scrape, in the city/region geography</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calculated_host_listings_count_shared_rooms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of Shared room listings the host has in the current scrape, in the city/region geography</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reviews_per_month</t>
   </si>
   <si>
     <t xml:space="preserve">The average number of reviews per month the listing has over the lifetime of the listing.
@@ -624,177 +487,351 @@
 </t>
   </si>
   <si>
-    <t>Change control</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Added</t>
-  </si>
-  <si>
-    <t>requires_license</t>
-  </si>
-  <si>
-    <t>[t=true; f=false]. Whether the listing/jurisdiction requires a license</t>
-  </si>
-  <si>
-    <t>jurisdiction_names</t>
-  </si>
-  <si>
-    <t>Legal jurisdiction</t>
-  </si>
-  <si>
-    <t>is_business_travel_ready</t>
-  </si>
-  <si>
-    <t>cancellation_policy</t>
-  </si>
-  <si>
-    <t>require_guest_profile_picture</t>
-  </si>
-  <si>
-    <t>require_guest_phone_verification</t>
-  </si>
-  <si>
-    <t>The number of reviews the listing has over the lifetime of the listing</t>
-  </si>
-  <si>
-    <t>Removed</t>
-  </si>
-  <si>
-    <t>Data Dictionary for listings.csv summary file</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Data Dictionary for reviews.csv data file</t>
-  </si>
-  <si>
-    <t>reviews.csv</t>
-  </si>
-  <si>
-    <t>neighbourhood_group</t>
-  </si>
-  <si>
-    <t>The reviews for each listing.</t>
-  </si>
-  <si>
-    <t>listing_id</t>
-  </si>
-  <si>
-    <t>daily price in local currency. Note, $ sign may be used despite locale</t>
-  </si>
-  <si>
-    <t>reviewer_id</t>
-  </si>
-  <si>
-    <t>reviewer_name</t>
-  </si>
-  <si>
-    <t>comments</t>
-  </si>
-  <si>
-    <t>avaliability_x. The availability of the listing x days in the future as determined by the calendar. Note a listing may be available because it has been booked by a guest or blocked by the host.</t>
-  </si>
-  <si>
-    <t>numeric (2 decimal places)</t>
-  </si>
-  <si>
-    <t>Data Dictionary for calendar.csv data file</t>
-  </si>
-  <si>
-    <t>calendar.csv</t>
-  </si>
-  <si>
-    <t>The calendar file records the price, availability and other details from the listing's calendar for each day of the next 365 days</t>
-  </si>
-  <si>
-    <t>The date in the listing's calendar</t>
-  </si>
-  <si>
-    <t>available</t>
-  </si>
-  <si>
-    <t>Whether the date is available for a booking</t>
-  </si>
-  <si>
-    <t>The price listed for the day</t>
-  </si>
-  <si>
-    <t>adjusted_price</t>
-  </si>
-  <si>
-    <t>Minimum nights for a booking made on this day</t>
-  </si>
-  <si>
-    <t>Maximum nights for a booking made on this day</t>
+    <t xml:space="preserve">Change control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of listings the host has (per Airbnb calculations)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daily price in local currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of reviews the listing has over the lifetime of the listing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Removed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">experiences_offered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">house_rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thumbnail_url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">medium_url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xl_picture_url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">street</t>
+  </si>
+  <si>
+    <t xml:space="preserve">city</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zipcode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smart_location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">country_code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_location_exact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bed_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">square_feet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weekly_price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monthly_price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">security_deposit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cleaning_fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">guests_included</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extra_people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">requires_license</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jurisdiction_names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_business_travel_ready</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cancellation_policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">require_guest_profile_picture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">require_guest_phone_verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary description of the listing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description of the space for rent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description of the experiences offered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes for the listing. In some cities, Airbnb instructs the host to write the legal Permit #, in liue of using the license_number field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes for the listing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL to the Airbnb hosted thumbnail image for the listing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL to the Airbnb hosted medium sized image for the listing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL to the Airbnb hosted XL sized image for the listing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of listings the host has</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[t=true; f=false]
+Possibly related to the host's choice for displaying the listing's location. See references.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.airbnb.com/help/article/2141/how-will-my-listings-location-be-shown-on-the-map
+https://www.airbnb.com/help/article/478/how-do-i-edit-my-listings-address-or-map-location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The type of bed(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weekly price in local currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monthly price in local currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">number of guests included in the price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amount in local currency for additional guests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[t=true; f=false]. Whether the listing/jurisdiction requires a license</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal jurisdiction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Dictionary for listings.csv summary file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neighbourhood_group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daily price in local currency. Note, $ sign may be used despite locale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avaliability_x. The availability of the listing x days in the future as determined by the calendar. Note a listing may be available because it has been booked by a guest or blocked by the host.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">numeric (2 decimal places)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Dictionary for reviews.csv data file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reviews.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The reviews for each listing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">listing_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reviewer_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reviewer_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Dictionary for calendar.csv data file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calendar.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The calendar file records the price, availability and other details from the listing's calendar for each day of the next 365 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The date in the listing's calendar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whether the date is available for a booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The price listed for the day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adjusted_price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum nights for a booking made on this day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum nights for a booking made on this day</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mmmm, yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="mmmm&quot;, &quot;yyyy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="14.0"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <u/>
-      <color rgb="FF0000FF"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="12.0"/>
+      <b val="true"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -802,150 +839,206 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF9900"/>
-        <bgColor rgb="FFFF9900"/>
+        <bgColor rgb="FFFFCC00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCFE2F3"/>
-        <bgColor rgb="FFCFE2F3"/>
+        <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FC5E8"/>
+        <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FC5E8"/>
-        <bgColor rgb="FF9FC5E8"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="17">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCFE2F3"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF9FC5E8"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -956,94 +1049,90 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4285f4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ea4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="fbbc04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="34a853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="ff6d01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="46bdc6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="1155cc"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="1155cc"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -1051,33 +1140,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -1090,13 +1170,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -1106,15 +1180,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -1122,7 +1194,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -1130,11 +1201,11 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1143,27 +1214,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E88"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="22.0"/>
-    <col customWidth="1" min="4" max="5" width="38.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="38.25"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1171,36 +1243,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="4" t="n">
         <v>4.7</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
-        <v>46082.0</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5" s="5" t="n">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
-    </row>
-    <row r="7">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
@@ -1217,7 +1292,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
@@ -1230,7 +1305,7 @@
       </c>
       <c r="E9" s="9"/>
     </row>
-    <row r="10">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
         <v>13</v>
       </c>
@@ -1243,7 +1318,7 @@
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
         <v>16</v>
       </c>
@@ -1258,7 +1333,7 @@
       </c>
       <c r="E11" s="9"/>
     </row>
-    <row r="12">
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
         <v>19</v>
       </c>
@@ -1273,87 +1348,87 @@
       </c>
       <c r="E12" s="9"/>
     </row>
-    <row r="13">
+    <row r="13" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="9" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E13" s="9"/>
     </row>
-    <row r="14">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E14" s="9"/>
     </row>
-    <row r="15">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E15" s="9"/>
     </row>
-    <row r="16">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E16" s="9"/>
     </row>
-    <row r="17">
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="9" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E17" s="9"/>
     </row>
-    <row r="18">
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="9" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E18" s="9"/>
     </row>
-    <row r="19">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>14</v>
@@ -1362,105 +1437,105 @@
         <v>15</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="E19" s="9"/>
     </row>
-    <row r="20">
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="9" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E20" s="9"/>
     </row>
-    <row r="21">
+    <row r="21" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="9" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E21" s="9"/>
     </row>
-    <row r="22">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="9" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="E22" s="9"/>
     </row>
-    <row r="23">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="9" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E23" s="9"/>
     </row>
-    <row r="24">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
     </row>
-    <row r="25">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
     </row>
-    <row r="26">
+    <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="9" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E26" s="9"/>
     </row>
-    <row r="27">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
     </row>
-    <row r="28">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>14</v>
@@ -1469,9 +1544,9 @@
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
     </row>
-    <row r="29">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>14</v>
@@ -1480,9 +1555,9 @@
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
-    <row r="30">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>14</v>
@@ -1491,66 +1566,66 @@
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
     </row>
-    <row r="31">
+    <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="9" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E31" s="9"/>
     </row>
-    <row r="32">
+    <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="9" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E32" s="9"/>
     </row>
-    <row r="33">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
     </row>
-    <row r="34">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
     </row>
-    <row r="35">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
     </row>
-    <row r="36">
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>14</v>
@@ -1559,9 +1634,9 @@
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
     </row>
-    <row r="37">
+    <row r="37" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>14</v>
@@ -1570,13 +1645,13 @@
         <v>15</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E37" s="9"/>
     </row>
-    <row r="38">
+    <row r="38" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>14</v>
@@ -1585,182 +1660,182 @@
         <v>15</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="E38" s="9"/>
     </row>
-    <row r="39">
+    <row r="39" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="9" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E39" s="9"/>
     </row>
-    <row r="40">
+    <row r="40" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="9" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E40" s="9"/>
     </row>
-    <row r="41">
+    <row r="41" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="9" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E41" s="9"/>
     </row>
-    <row r="42">
+    <row r="42" customFormat="false" ht="521.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>72</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="9" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E43" s="9"/>
     </row>
-    <row r="44">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="9" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="E44" s="9"/>
     </row>
-    <row r="45">
+    <row r="45" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="9" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E45" s="9"/>
     </row>
-    <row r="46">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="9" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="E46" s="9"/>
     </row>
-    <row r="47">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="9" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="E47" s="9"/>
     </row>
-    <row r="48">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
     </row>
-    <row r="49">
+    <row r="49" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C49" s="12"/>
+        <v>88</v>
+      </c>
+      <c r="C49" s="8"/>
       <c r="D49" s="9" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="E49" s="9"/>
     </row>
-    <row r="50">
+    <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="9" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="E50" s="9"/>
     </row>
-    <row r="51">
+    <row r="51" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="9" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="E51" s="9"/>
     </row>
-    <row r="52">
+    <row r="52" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>11</v>
@@ -1769,13 +1844,13 @@
         <v>15</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="E52" s="9"/>
     </row>
-    <row r="53">
+    <row r="53" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>11</v>
@@ -1784,13 +1859,13 @@
         <v>15</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="E53" s="9"/>
     </row>
-    <row r="54">
+    <row r="54" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>11</v>
@@ -1799,13 +1874,13 @@
         <v>15</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="E54" s="9"/>
     </row>
-    <row r="55">
+    <row r="55" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>11</v>
@@ -1814,67 +1889,67 @@
         <v>15</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="E55" s="9"/>
     </row>
-    <row r="56">
+    <row r="56" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="E56" s="9"/>
     </row>
-    <row r="57">
+    <row r="57" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="E57" s="9"/>
     </row>
-    <row r="58">
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
     </row>
-    <row r="59">
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="9" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="E59" s="9"/>
     </row>
-    <row r="60">
+    <row r="60" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>11</v>
@@ -1883,13 +1958,13 @@
         <v>15</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E60" s="9"/>
     </row>
-    <row r="61">
+    <row r="61" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>11</v>
@@ -1898,13 +1973,13 @@
         <v>15</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E61" s="9"/>
     </row>
-    <row r="62">
+    <row r="62" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>11</v>
@@ -1913,13 +1988,13 @@
         <v>15</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E62" s="9"/>
     </row>
-    <row r="63">
+    <row r="63" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>11</v>
@@ -1928,37 +2003,37 @@
         <v>15</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E63" s="9"/>
     </row>
-    <row r="64">
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C64" s="12"/>
+        <v>39</v>
+      </c>
+      <c r="C64" s="8"/>
       <c r="D64" s="9"/>
       <c r="E64" s="9"/>
     </row>
-    <row r="65">
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="8"/>
       <c r="D65" s="9" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="E65" s="9"/>
     </row>
-    <row r="66">
+    <row r="66" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>11</v>
@@ -1967,13 +2042,13 @@
         <v>15</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="E66" s="9"/>
     </row>
-    <row r="67">
+    <row r="67" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>11</v>
@@ -1982,132 +2057,132 @@
         <v>15</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>169</v>
+        <v>121</v>
       </c>
       <c r="E67" s="9"/>
     </row>
-    <row r="68">
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="E68" s="9"/>
     </row>
-    <row r="69">
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>173</v>
+        <v>125</v>
       </c>
       <c r="E69" s="9"/>
     </row>
-    <row r="70">
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>174</v>
+        <v>126</v>
       </c>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
       <c r="D70" s="9"/>
       <c r="E70" s="9"/>
     </row>
-    <row r="71">
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
     </row>
-    <row r="72">
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
     </row>
-    <row r="73">
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
     </row>
-    <row r="74">
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>178</v>
+        <v>130</v>
       </c>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
     </row>
-    <row r="75">
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
     </row>
-    <row r="76">
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="s">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
       <c r="D76" s="9"/>
       <c r="E76" s="9"/>
     </row>
-    <row r="77">
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="B77" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="9" t="s">
-        <v>182</v>
+        <v>134</v>
       </c>
       <c r="E77" s="9"/>
     </row>
-    <row r="78">
+    <row r="78" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="9" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="E78" s="9"/>
     </row>
-    <row r="79">
+    <row r="79" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="s">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>11</v>
@@ -2116,13 +2191,13 @@
         <v>15</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>186</v>
+        <v>138</v>
       </c>
       <c r="E79" s="9"/>
     </row>
-    <row r="80">
+    <row r="80" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>11</v>
@@ -2131,13 +2206,13 @@
         <v>15</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="E80" s="9"/>
     </row>
-    <row r="81">
+    <row r="81" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="s">
-        <v>189</v>
+        <v>141</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>11</v>
@@ -2146,13 +2221,13 @@
         <v>15</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>190</v>
+        <v>142</v>
       </c>
       <c r="E81" s="9"/>
     </row>
-    <row r="82">
+    <row r="82" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="s">
-        <v>191</v>
+        <v>143</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>11</v>
@@ -2161,47 +2236,47 @@
         <v>15</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>192</v>
+        <v>144</v>
       </c>
       <c r="E82" s="9"/>
     </row>
-    <row r="83">
+    <row r="83" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="s">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
       <c r="E83" s="9"/>
     </row>
-    <row r="85">
-      <c r="A85" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="14" t="s">
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B86" s="14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="15" t="s">
-        <v>30</v>
+      <c r="B86" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="8"/>
     </row>
   </sheetData>
@@ -2209,34 +2284,41 @@
     <mergeCell ref="B6:E6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="E42"/>
+    <hyperlink ref="E42" r:id="rId1" display="https://www.airbnb.com/help/article/5/what-does-the-room-type-of-a-listing-mean"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E88"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="22.0"/>
-    <col customWidth="1" min="4" max="5" width="38.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="38.25"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -2244,36 +2326,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="4" t="n">
         <v>4.3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
-        <v>44774.0</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5" s="5" t="n">
+        <v>44774</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
-    </row>
-    <row r="7">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
@@ -2290,7 +2375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
@@ -2303,7 +2388,7 @@
       </c>
       <c r="E9" s="9"/>
     </row>
-    <row r="10">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
         <v>13</v>
       </c>
@@ -2316,7 +2401,7 @@
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2331,7 +2416,7 @@
       </c>
       <c r="E11" s="9"/>
     </row>
-    <row r="12">
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
         <v>19</v>
       </c>
@@ -2346,87 +2431,87 @@
       </c>
       <c r="E12" s="9"/>
     </row>
-    <row r="13">
+    <row r="13" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="9" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E13" s="9"/>
     </row>
-    <row r="14">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E14" s="9"/>
     </row>
-    <row r="15">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E15" s="9"/>
     </row>
-    <row r="16">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E16" s="9"/>
     </row>
-    <row r="17">
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="9" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E17" s="9"/>
     </row>
-    <row r="18">
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="9" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E18" s="9"/>
     </row>
-    <row r="19">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>14</v>
@@ -2435,105 +2520,105 @@
         <v>15</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="E19" s="9"/>
     </row>
-    <row r="20">
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="9" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E20" s="9"/>
     </row>
-    <row r="21">
+    <row r="21" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="9" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E21" s="9"/>
     </row>
-    <row r="22">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="9" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="E22" s="9"/>
     </row>
-    <row r="23">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="9" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E23" s="9"/>
     </row>
-    <row r="24">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
     </row>
-    <row r="25">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
     </row>
-    <row r="26">
+    <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="9" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E26" s="9"/>
     </row>
-    <row r="27">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
     </row>
-    <row r="28">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>14</v>
@@ -2542,9 +2627,9 @@
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
     </row>
-    <row r="29">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>14</v>
@@ -2553,9 +2638,9 @@
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
-    <row r="30">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>14</v>
@@ -2564,66 +2649,66 @@
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
     </row>
-    <row r="31">
+    <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="9" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E31" s="9"/>
     </row>
-    <row r="32">
+    <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="9" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E32" s="9"/>
     </row>
-    <row r="33">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
     </row>
-    <row r="34">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
     </row>
-    <row r="35">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
     </row>
-    <row r="36">
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>14</v>
@@ -2632,9 +2717,9 @@
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
     </row>
-    <row r="37">
+    <row r="37" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>14</v>
@@ -2643,13 +2728,13 @@
         <v>15</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E37" s="9"/>
     </row>
-    <row r="38">
+    <row r="38" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>14</v>
@@ -2658,182 +2743,182 @@
         <v>15</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="E38" s="9"/>
     </row>
-    <row r="39">
+    <row r="39" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="9" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E39" s="9"/>
     </row>
-    <row r="40">
+    <row r="40" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="9" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E40" s="9"/>
     </row>
-    <row r="41">
+    <row r="41" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="9" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E41" s="9"/>
     </row>
-    <row r="42">
+    <row r="42" customFormat="false" ht="521.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>72</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="9" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E43" s="9"/>
     </row>
-    <row r="44">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="9" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="E44" s="9"/>
     </row>
-    <row r="45">
+    <row r="45" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="9" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E45" s="9"/>
     </row>
-    <row r="46">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="9" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="E46" s="9"/>
     </row>
-    <row r="47">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="9" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="E47" s="9"/>
     </row>
-    <row r="48">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
     </row>
-    <row r="49">
+    <row r="49" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C49" s="12"/>
+        <v>88</v>
+      </c>
+      <c r="C49" s="8"/>
       <c r="D49" s="9" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="E49" s="9"/>
     </row>
-    <row r="50">
+    <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="9" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="E50" s="9"/>
     </row>
-    <row r="51">
+    <row r="51" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="9" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="E51" s="9"/>
     </row>
-    <row r="52">
+    <row r="52" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>11</v>
@@ -2842,13 +2927,13 @@
         <v>15</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="E52" s="9"/>
     </row>
-    <row r="53">
+    <row r="53" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>11</v>
@@ -2857,13 +2942,13 @@
         <v>15</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="E53" s="9"/>
     </row>
-    <row r="54">
+    <row r="54" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>11</v>
@@ -2872,13 +2957,13 @@
         <v>15</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="E54" s="9"/>
     </row>
-    <row r="55">
+    <row r="55" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>11</v>
@@ -2887,67 +2972,67 @@
         <v>15</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="E55" s="9"/>
     </row>
-    <row r="56">
+    <row r="56" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="E56" s="9"/>
     </row>
-    <row r="57">
+    <row r="57" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="E57" s="9"/>
     </row>
-    <row r="58">
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
     </row>
-    <row r="59">
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="9" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="E59" s="9"/>
     </row>
-    <row r="60">
+    <row r="60" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>11</v>
@@ -2956,13 +3041,13 @@
         <v>15</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E60" s="9"/>
     </row>
-    <row r="61">
+    <row r="61" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>11</v>
@@ -2971,13 +3056,13 @@
         <v>15</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E61" s="9"/>
     </row>
-    <row r="62">
+    <row r="62" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>11</v>
@@ -2986,13 +3071,13 @@
         <v>15</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E62" s="9"/>
     </row>
-    <row r="63">
+    <row r="63" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>11</v>
@@ -3001,37 +3086,37 @@
         <v>15</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E63" s="9"/>
     </row>
-    <row r="64">
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C64" s="12"/>
+        <v>39</v>
+      </c>
+      <c r="C64" s="8"/>
       <c r="D64" s="9"/>
       <c r="E64" s="9"/>
     </row>
-    <row r="65">
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="8"/>
       <c r="D65" s="9" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="E65" s="9"/>
     </row>
-    <row r="66">
+    <row r="66" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>11</v>
@@ -3040,13 +3125,13 @@
         <v>15</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="E66" s="9"/>
     </row>
-    <row r="67">
+    <row r="67" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>11</v>
@@ -3055,132 +3140,132 @@
         <v>15</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>169</v>
+        <v>121</v>
       </c>
       <c r="E67" s="9"/>
     </row>
-    <row r="68">
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="E68" s="9"/>
     </row>
-    <row r="69">
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>173</v>
+        <v>125</v>
       </c>
       <c r="E69" s="9"/>
     </row>
-    <row r="70">
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>174</v>
+        <v>126</v>
       </c>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
       <c r="D70" s="9"/>
       <c r="E70" s="9"/>
     </row>
-    <row r="71">
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
     </row>
-    <row r="72">
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
     </row>
-    <row r="73">
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
     </row>
-    <row r="74">
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>178</v>
+        <v>130</v>
       </c>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
     </row>
-    <row r="75">
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
     </row>
-    <row r="76">
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="s">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
       <c r="D76" s="9"/>
       <c r="E76" s="9"/>
     </row>
-    <row r="77">
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="B77" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="9" t="s">
-        <v>182</v>
+        <v>134</v>
       </c>
       <c r="E77" s="9"/>
     </row>
-    <row r="78">
+    <row r="78" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="9" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="E78" s="9"/>
     </row>
-    <row r="79">
+    <row r="79" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="s">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>11</v>
@@ -3189,13 +3274,13 @@
         <v>15</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>186</v>
+        <v>138</v>
       </c>
       <c r="E79" s="9"/>
     </row>
-    <row r="80">
+    <row r="80" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>11</v>
@@ -3204,13 +3289,13 @@
         <v>15</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="E80" s="9"/>
     </row>
-    <row r="81">
+    <row r="81" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="s">
-        <v>189</v>
+        <v>141</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>11</v>
@@ -3219,13 +3304,13 @@
         <v>15</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>190</v>
+        <v>142</v>
       </c>
       <c r="E81" s="9"/>
     </row>
-    <row r="82">
+    <row r="82" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="s">
-        <v>191</v>
+        <v>143</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>11</v>
@@ -3234,47 +3319,47 @@
         <v>15</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>192</v>
+        <v>144</v>
       </c>
       <c r="E82" s="9"/>
     </row>
-    <row r="83">
+    <row r="83" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="s">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
       <c r="E83" s="9"/>
     </row>
-    <row r="85">
-      <c r="A85" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="14" t="s">
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B86" s="14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="15" t="s">
-        <v>30</v>
+      <c r="B86" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="8"/>
     </row>
   </sheetData>
@@ -3282,34 +3367,41 @@
     <mergeCell ref="B6:E6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="E42"/>
+    <hyperlink ref="E42" r:id="rId1" display="https://www.airbnb.com/help/article/5/what-does-the-room-type-of-a-listing-mean"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E130"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="22.0"/>
-    <col customWidth="1" min="4" max="5" width="38.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="38.25"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -3317,36 +3409,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
-        <v>44044.0</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5" s="5" t="n">
+        <v>44044</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
-    </row>
-    <row r="7">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
@@ -3363,7 +3458,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
@@ -3376,7 +3471,7 @@
       </c>
       <c r="E9" s="9"/>
     </row>
-    <row r="10">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
         <v>13</v>
       </c>
@@ -3389,7 +3484,7 @@
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
         <v>16</v>
       </c>
@@ -3404,7 +3499,7 @@
       </c>
       <c r="E11" s="9"/>
     </row>
-    <row r="12">
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
         <v>19</v>
       </c>
@@ -3419,74 +3514,74 @@
       </c>
       <c r="E12" s="9"/>
     </row>
-    <row r="13">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E13" s="9"/>
     </row>
-    <row r="14">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E14" s="9"/>
     </row>
-    <row r="15">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E15" s="9"/>
     </row>
-    <row r="16">
+    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="9" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E16" s="9"/>
     </row>
-    <row r="17">
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="9" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E17" s="9"/>
     </row>
-    <row r="18">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>14</v>
@@ -3495,105 +3590,105 @@
         <v>15</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="E18" s="9"/>
     </row>
-    <row r="19">
+    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="9" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E19" s="9"/>
     </row>
-    <row r="20">
+    <row r="20" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="9" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E20" s="9"/>
     </row>
-    <row r="21">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="9" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="E21" s="9"/>
     </row>
-    <row r="22">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="9" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E22" s="9"/>
     </row>
-    <row r="23">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="24">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
     </row>
-    <row r="25">
+    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="9" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E25" s="9"/>
     </row>
-    <row r="26">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
     </row>
-    <row r="27">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>14</v>
@@ -3602,9 +3697,9 @@
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
     </row>
-    <row r="28">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>14</v>
@@ -3613,9 +3708,9 @@
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
     </row>
-    <row r="29">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>14</v>
@@ -3624,66 +3719,66 @@
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
     </row>
-    <row r="30">
+    <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="9" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="E30" s="9"/>
     </row>
-    <row r="31">
+    <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="9" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="E31" s="9"/>
     </row>
-    <row r="32">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
     </row>
-    <row r="33">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
     </row>
-    <row r="34">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
     </row>
-    <row r="35">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>14</v>
@@ -3692,9 +3787,9 @@
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
     </row>
-    <row r="36">
+    <row r="36" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>14</v>
@@ -3703,13 +3798,13 @@
         <v>15</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E36" s="9"/>
     </row>
-    <row r="37">
+    <row r="37" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>14</v>
@@ -3718,182 +3813,182 @@
         <v>15</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="E37" s="9"/>
     </row>
-    <row r="38">
+    <row r="38" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="9" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E38" s="9"/>
     </row>
-    <row r="39">
+    <row r="39" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="9" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E39" s="9"/>
     </row>
-    <row r="40">
+    <row r="40" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="9" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E40" s="9"/>
     </row>
-    <row r="41">
+    <row r="41" customFormat="false" ht="521.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>72</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="9" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E42" s="9"/>
     </row>
-    <row r="43">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="9" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="E43" s="9"/>
     </row>
-    <row r="44">
+    <row r="44" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="9" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E44" s="9"/>
     </row>
-    <row r="45">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="9" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="E45" s="9"/>
     </row>
-    <row r="46">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="9" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="E46" s="9"/>
     </row>
-    <row r="47">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
     </row>
-    <row r="48">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C48" s="12"/>
+        <v>88</v>
+      </c>
+      <c r="C48" s="8"/>
       <c r="D48" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E48" s="9"/>
     </row>
-    <row r="49">
+    <row r="49" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="9" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="E49" s="9"/>
     </row>
-    <row r="50">
+    <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="9" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="E50" s="9"/>
     </row>
-    <row r="51">
+    <row r="51" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>11</v>
@@ -3902,13 +3997,13 @@
         <v>15</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="E51" s="9"/>
     </row>
-    <row r="52">
+    <row r="52" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>11</v>
@@ -3917,13 +4012,13 @@
         <v>15</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="E52" s="9"/>
     </row>
-    <row r="53">
+    <row r="53" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>11</v>
@@ -3932,13 +4027,13 @@
         <v>15</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="E53" s="9"/>
     </row>
-    <row r="54">
+    <row r="54" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>11</v>
@@ -3947,67 +4042,67 @@
         <v>15</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="E54" s="9"/>
     </row>
-    <row r="55">
+    <row r="55" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="E55" s="9"/>
     </row>
-    <row r="56">
+    <row r="56" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="E56" s="9"/>
     </row>
-    <row r="57">
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
     </row>
-    <row r="58">
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="9" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="E58" s="9"/>
     </row>
-    <row r="59">
+    <row r="59" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="B59" s="8" t="s">
         <v>11</v>
@@ -4016,13 +4111,13 @@
         <v>15</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E59" s="9"/>
     </row>
-    <row r="60">
+    <row r="60" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>11</v>
@@ -4031,13 +4126,13 @@
         <v>15</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E60" s="9"/>
     </row>
-    <row r="61">
+    <row r="61" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>11</v>
@@ -4046,13 +4141,13 @@
         <v>15</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E61" s="9"/>
     </row>
-    <row r="62">
+    <row r="62" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>11</v>
@@ -4061,37 +4156,37 @@
         <v>15</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E62" s="9"/>
     </row>
-    <row r="63">
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C63" s="12"/>
+        <v>39</v>
+      </c>
+      <c r="C63" s="8"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
     </row>
-    <row r="64">
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="B64" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="9" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="E64" s="9"/>
     </row>
-    <row r="65">
+    <row r="65" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>11</v>
@@ -4100,13 +4195,13 @@
         <v>15</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="E65" s="9"/>
     </row>
-    <row r="66">
+    <row r="66" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>11</v>
@@ -4115,530 +4210,530 @@
         <v>15</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>169</v>
+        <v>121</v>
       </c>
       <c r="E66" s="9"/>
     </row>
-    <row r="67">
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="E67" s="9"/>
     </row>
-    <row r="68">
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>173</v>
+        <v>125</v>
       </c>
       <c r="E68" s="9"/>
     </row>
-    <row r="69">
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>174</v>
+        <v>126</v>
       </c>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
     </row>
-    <row r="70">
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
       <c r="D70" s="9"/>
       <c r="E70" s="9"/>
     </row>
-    <row r="71">
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
     </row>
-    <row r="72">
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
     </row>
-    <row r="73">
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>178</v>
+        <v>130</v>
       </c>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
     </row>
-    <row r="74">
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
     </row>
-    <row r="75">
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
     </row>
-    <row r="76">
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C76" s="8"/>
       <c r="D76" s="9" t="s">
-        <v>182</v>
+        <v>134</v>
       </c>
       <c r="E76" s="9"/>
     </row>
-    <row r="77">
+    <row r="77" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E77" s="9"/>
+    </row>
+    <row r="78" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E78" s="9"/>
+    </row>
+    <row r="79" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E79" s="9"/>
+    </row>
+    <row r="80" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E80" s="9"/>
+    </row>
+    <row r="81" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E81" s="9"/>
+    </row>
+    <row r="82" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E82" s="9"/>
+    </row>
+    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E77" s="9"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="8" t="s">
+      <c r="B116" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="B78" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D78" s="9" t="s">
+      <c r="B117" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="E78" s="9"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="8" t="s">
+      <c r="B118" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B79" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="E79" s="9"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="E80" s="9"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="B81" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="E81" s="9"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="E82" s="9"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B85" s="14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="18" t="s">
-        <v>205</v>
-      </c>
       <c r="B119" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="120">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="8" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="121">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="8" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="122">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="8"/>
     </row>
-    <row r="123">
+    <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="8"/>
     </row>
-    <row r="124">
+    <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="8"/>
     </row>
-    <row r="125">
+    <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="8"/>
     </row>
-    <row r="126">
+    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="8"/>
     </row>
-    <row r="127">
+    <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="8"/>
     </row>
-    <row r="128">
+    <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="8"/>
     </row>
-    <row r="129">
+    <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="8"/>
     </row>
-    <row r="130">
+    <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="8"/>
     </row>
   </sheetData>
@@ -4646,34 +4741,41 @@
     <mergeCell ref="B6:E6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="E41"/>
+    <hyperlink ref="E41" r:id="rId1" display="https://www.airbnb.com/help/article/5/what-does-the-room-type-of-a-listing-mean"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E127"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="22.0"/>
-    <col customWidth="1" min="4" max="5" width="38.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="38.25"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -4681,36 +4783,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
-        <v>2019.0</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5" s="4" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
-    </row>
-    <row r="7">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
@@ -4727,7 +4832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
@@ -4740,7 +4845,7 @@
       </c>
       <c r="E9" s="9"/>
     </row>
-    <row r="10">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
         <v>13</v>
       </c>
@@ -4753,7 +4858,7 @@
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
     </row>
-    <row r="11">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
         <v>16</v>
       </c>
@@ -4768,7 +4873,7 @@
       </c>
       <c r="E11" s="9"/>
     </row>
-    <row r="12">
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
         <v>19</v>
       </c>
@@ -4783,126 +4888,126 @@
       </c>
       <c r="E12" s="9"/>
     </row>
-    <row r="13">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E13" s="9"/>
     </row>
-    <row r="14">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="9" t="s">
-        <v>25</v>
+        <v>188</v>
       </c>
       <c r="E14" s="9"/>
     </row>
-    <row r="15">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="9" t="s">
-        <v>27</v>
+        <v>189</v>
       </c>
       <c r="E15" s="9"/>
     </row>
-    <row r="16">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E16" s="9"/>
     </row>
-    <row r="17">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="9" t="s">
-        <v>33</v>
+        <v>190</v>
       </c>
       <c r="E17" s="9"/>
     </row>
-    <row r="18">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E18" s="9"/>
     </row>
-    <row r="19">
+    <row r="19" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="9" t="s">
-        <v>37</v>
+        <v>191</v>
       </c>
       <c r="E19" s="9"/>
     </row>
-    <row r="20">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>38</v>
+        <v>158</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="9" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="E20" s="9"/>
     </row>
-    <row r="21">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="9" t="s">
-        <v>41</v>
+        <v>193</v>
       </c>
       <c r="E21" s="9"/>
     </row>
-    <row r="22">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>14</v>
@@ -4911,9 +5016,9 @@
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
     </row>
-    <row r="23">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>43</v>
+        <v>161</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>14</v>
@@ -4922,74 +5027,74 @@
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="24">
+    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>44</v>
+        <v>162</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="9" t="s">
-        <v>45</v>
+        <v>194</v>
       </c>
       <c r="E24" s="9"/>
     </row>
-    <row r="25">
+    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="9" t="s">
-        <v>64</v>
+        <v>195</v>
       </c>
       <c r="E25" s="9"/>
     </row>
-    <row r="26">
+    <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="9" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E26" s="9"/>
     </row>
-    <row r="27">
+    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="9" t="s">
-        <v>71</v>
+        <v>196</v>
       </c>
       <c r="E27" s="9"/>
     </row>
-    <row r="28">
+    <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="9" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E28" s="9"/>
     </row>
-    <row r="29">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>14</v>
@@ -4998,105 +5103,105 @@
         <v>15</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="E29" s="9"/>
     </row>
-    <row r="30">
+    <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="9" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E30" s="9"/>
     </row>
-    <row r="31">
+    <row r="31" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="9" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E31" s="9"/>
     </row>
-    <row r="32">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="9" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="E32" s="9"/>
     </row>
-    <row r="33">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="9" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E33" s="9"/>
     </row>
-    <row r="34">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
     </row>
-    <row r="35">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
     </row>
-    <row r="36">
+    <row r="36" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
       <c r="D36" s="9" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E36" s="9"/>
     </row>
-    <row r="37">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
     </row>
-    <row r="38">
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>14</v>
@@ -5105,9 +5210,9 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
     </row>
-    <row r="39">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>14</v>
@@ -5116,9 +5221,9 @@
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
     </row>
-    <row r="40">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>14</v>
@@ -5127,66 +5232,66 @@
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
     </row>
-    <row r="41">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="9" t="s">
-        <v>95</v>
+        <v>197</v>
       </c>
       <c r="E41" s="9"/>
     </row>
-    <row r="42">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="9" t="s">
-        <v>95</v>
+        <v>197</v>
       </c>
       <c r="E42" s="9"/>
     </row>
-    <row r="43">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
     </row>
-    <row r="44">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
     </row>
-    <row r="45">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
     </row>
-    <row r="46">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>96</v>
+        <v>165</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>14</v>
@@ -5195,9 +5300,9 @@
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
     </row>
-    <row r="47">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>14</v>
@@ -5206,9 +5311,9 @@
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
     </row>
-    <row r="48">
+    <row r="48" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>14</v>
@@ -5217,13 +5322,13 @@
         <v>15</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E48" s="9"/>
     </row>
-    <row r="49">
+    <row r="49" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>14</v>
@@ -5232,13 +5337,13 @@
         <v>15</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="E49" s="9"/>
     </row>
-    <row r="50">
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>97</v>
+        <v>166</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>14</v>
@@ -5247,9 +5352,9 @@
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
     </row>
-    <row r="51">
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>98</v>
+        <v>167</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>14</v>
@@ -5258,9 +5363,9 @@
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
     </row>
-    <row r="52">
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>14</v>
@@ -5269,9 +5374,9 @@
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
     </row>
-    <row r="53">
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>14</v>
@@ -5280,9 +5385,9 @@
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
     </row>
-    <row r="54">
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>101</v>
+        <v>170</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>14</v>
@@ -5291,9 +5396,9 @@
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
     </row>
-    <row r="55">
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>102</v>
+        <v>171</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>14</v>
@@ -5302,9 +5407,9 @@
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
     </row>
-    <row r="56">
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>14</v>
@@ -5313,154 +5418,154 @@
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
     </row>
-    <row r="57">
+    <row r="57" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="9" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E57" s="9"/>
     </row>
-    <row r="58">
+    <row r="58" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="9" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E58" s="9"/>
     </row>
-    <row r="59">
+    <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C59" s="8"/>
-      <c r="D59" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="60">
+      <c r="D59" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C60" s="8"/>
       <c r="D60" s="9" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E60" s="9"/>
     </row>
-    <row r="61">
+    <row r="61" customFormat="false" ht="521.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E61" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>72</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="8"/>
       <c r="D62" s="9" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E62" s="9"/>
     </row>
-    <row r="63">
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C63" s="8"/>
       <c r="D63" s="9" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="E63" s="9"/>
     </row>
-    <row r="64">
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="B64" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="9" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="E64" s="9"/>
     </row>
-    <row r="65">
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="8"/>
       <c r="D65" s="9" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="E65" s="9"/>
     </row>
-    <row r="66">
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C66" s="8"/>
       <c r="D66" s="9" t="s">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="E66" s="9"/>
     </row>
-    <row r="67">
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="9"/>
       <c r="E67" s="9"/>
     </row>
-    <row r="68">
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="B68" s="8" t="s">
         <v>11</v>
@@ -5469,122 +5574,122 @@
       <c r="D68" s="9"/>
       <c r="E68" s="9"/>
     </row>
-    <row r="69">
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C69" s="12"/>
+        <v>88</v>
+      </c>
+      <c r="C69" s="8"/>
       <c r="D69" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E69" s="9"/>
     </row>
-    <row r="70">
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C70" s="12"/>
+        <v>88</v>
+      </c>
+      <c r="C70" s="8"/>
       <c r="D70" s="9" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="E70" s="9"/>
     </row>
-    <row r="71">
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C71" s="12"/>
+        <v>88</v>
+      </c>
+      <c r="C71" s="8"/>
       <c r="D71" s="9" t="s">
-        <v>155</v>
+        <v>202</v>
       </c>
       <c r="E71" s="9"/>
     </row>
-    <row r="72">
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="C72" s="8"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
     </row>
-    <row r="73">
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="C73" s="8"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
     </row>
-    <row r="74">
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
       <c r="C74" s="8"/>
       <c r="D74" s="9" t="s">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="E74" s="9"/>
     </row>
-    <row r="75">
+    <row r="75" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="C75" s="8"/>
       <c r="D75" s="9" t="s">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="E75" s="9"/>
     </row>
-    <row r="76">
+    <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="8"/>
       <c r="D76" s="9" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="E76" s="9"/>
     </row>
-    <row r="77">
+    <row r="77" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="B77" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="9" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="E77" s="9"/>
     </row>
-    <row r="78">
+    <row r="78" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="B78" s="8" t="s">
         <v>11</v>
@@ -5593,13 +5698,13 @@
         <v>15</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="E78" s="9"/>
     </row>
-    <row r="79">
+    <row r="79" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>11</v>
@@ -5608,13 +5713,13 @@
         <v>15</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="E79" s="9"/>
     </row>
-    <row r="80">
+    <row r="80" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>11</v>
@@ -5623,13 +5728,13 @@
         <v>15</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="E80" s="9"/>
     </row>
-    <row r="81">
+    <row r="81" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>11</v>
@@ -5638,63 +5743,63 @@
         <v>15</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="E81" s="9"/>
     </row>
-    <row r="82">
+    <row r="82" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="B82" s="8"/>
       <c r="C82" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="E82" s="9"/>
     </row>
-    <row r="83">
+    <row r="83" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="B83" s="8"/>
       <c r="C83" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="E83" s="9"/>
     </row>
-    <row r="84">
+    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C84" s="8"/>
       <c r="D84" s="9"/>
       <c r="E84" s="9"/>
     </row>
-    <row r="85">
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C85" s="8"/>
       <c r="D85" s="9" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="E85" s="9"/>
     </row>
-    <row r="86">
+    <row r="86" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="8" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>11</v>
@@ -5703,13 +5808,13 @@
         <v>15</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E86" s="9"/>
     </row>
-    <row r="87">
+    <row r="87" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="8" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>11</v>
@@ -5718,13 +5823,13 @@
         <v>15</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E87" s="9"/>
     </row>
-    <row r="88">
+    <row r="88" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="8" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>11</v>
@@ -5733,13 +5838,13 @@
         <v>15</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E88" s="9"/>
     </row>
-    <row r="89">
+    <row r="89" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="8" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="B89" s="8" t="s">
         <v>11</v>
@@ -5748,37 +5853,37 @@
         <v>15</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="E89" s="9"/>
     </row>
-    <row r="90">
+    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C90" s="12"/>
+        <v>39</v>
+      </c>
+      <c r="C90" s="8"/>
       <c r="D90" s="9"/>
       <c r="E90" s="9"/>
     </row>
-    <row r="91">
+    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="B91" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C91" s="8"/>
       <c r="D91" s="9" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="E91" s="9"/>
     </row>
-    <row r="92">
+    <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="B92" s="8" t="s">
         <v>11</v>
@@ -5787,369 +5892,369 @@
         <v>15</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="E92" s="9"/>
     </row>
-    <row r="93">
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="s">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="E93" s="9"/>
     </row>
-    <row r="94">
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="8" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>173</v>
+        <v>125</v>
       </c>
       <c r="E94" s="9"/>
     </row>
-    <row r="95">
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="s">
-        <v>174</v>
+        <v>126</v>
       </c>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
       <c r="D95" s="9"/>
       <c r="E95" s="9"/>
     </row>
-    <row r="96">
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="8" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
       <c r="D96" s="9"/>
       <c r="E96" s="9"/>
     </row>
-    <row r="97">
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
       <c r="D97" s="9"/>
       <c r="E97" s="9"/>
     </row>
-    <row r="98">
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="8" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
       <c r="D98" s="9"/>
       <c r="E98" s="9"/>
     </row>
-    <row r="99">
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="8" t="s">
-        <v>178</v>
+        <v>130</v>
       </c>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
       <c r="D99" s="9"/>
       <c r="E99" s="9"/>
     </row>
-    <row r="100">
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="8" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
       <c r="D100" s="9"/>
       <c r="E100" s="9"/>
     </row>
-    <row r="101">
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="8" t="s">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
       <c r="D101" s="9"/>
       <c r="E101" s="9"/>
     </row>
-    <row r="102">
+    <row r="102" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="8" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C102" s="8"/>
       <c r="D102" s="9" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E102" s="9"/>
     </row>
-    <row r="103">
+    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="8" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="B103" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C103" s="8"/>
       <c r="D103" s="9" t="s">
-        <v>182</v>
+        <v>134</v>
       </c>
       <c r="E103" s="9"/>
     </row>
-    <row r="104">
+    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="8" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C104" s="8"/>
       <c r="D104" s="9" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E104" s="9"/>
     </row>
-    <row r="105">
+    <row r="105" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="8" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C105" s="8"/>
       <c r="D105" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E105" s="9"/>
+    </row>
+    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E105" s="9"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="8" t="s">
-        <v>202</v>
-      </c>
       <c r="B106" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C106" s="8"/>
       <c r="D106" s="9" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="E106" s="9"/>
     </row>
-    <row r="107">
+    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="8" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
       <c r="D107" s="9"/>
       <c r="E107" s="9"/>
     </row>
-    <row r="108">
+    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="8" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C108" s="8"/>
-      <c r="D108" s="16" t="s">
+      <c r="D108" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E108" s="14"/>
+    </row>
+    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C109" s="8"/>
+      <c r="D109" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E109" s="14"/>
+    </row>
+    <row r="110" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E110" s="9"/>
+    </row>
+    <row r="111" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E111" s="9"/>
+    </row>
+    <row r="112" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E112" s="9"/>
+    </row>
+    <row r="113" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D113" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="E108" s="16"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="B109" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C109" s="8"/>
-      <c r="D109" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="E109" s="16"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="B110" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="E110" s="9"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="B111" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D111" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="E111" s="9"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="B112" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="E112" s="9"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="B113" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>192</v>
-      </c>
       <c r="E113" s="9"/>
     </row>
-    <row r="114">
+    <row r="114" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="8" t="s">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>206</v>
+        <v>152</v>
       </c>
       <c r="E114" s="9"/>
     </row>
-    <row r="116">
-      <c r="A116" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="14" t="s">
+    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B117" s="14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="118">
+      <c r="B117" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="119">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="120">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="121">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="122">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="123">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="124">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="125">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="126">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>189</v>
+        <v>141</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="127">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>191</v>
+        <v>143</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>197</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -6157,34 +6262,41 @@
     <mergeCell ref="B6:E6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="E61"/>
+    <hyperlink ref="E61" r:id="rId1" display="https://www.airbnb.com/help/article/5/what-does-the-room-type-of-a-listing-mean"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="27.5"/>
-    <col customWidth="1" min="4" max="4" width="28.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28.38"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>208</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -6192,15 +6304,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -6208,20 +6320,23 @@
         <v>209</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
-    </row>
-    <row r="7">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
@@ -6238,51 +6353,51 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="12"/>
+      <c r="C9" s="8"/>
       <c r="D9" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-    </row>
-    <row r="11">
+        <v>79</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-    </row>
-    <row r="12">
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-    </row>
-    <row r="13">
+        <v>79</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>14</v>
@@ -6291,12 +6406,12 @@
         <v>15</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>14</v>
@@ -6305,94 +6420,94 @@
         <v>15</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" s="12"/>
+        <v>66</v>
+      </c>
+      <c r="C15" s="8"/>
       <c r="D15" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+    </row>
+    <row r="18" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="s">
+      <c r="B18" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="12"/>
+      <c r="C18" s="8"/>
       <c r="D18" s="9" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="9" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>11</v>
@@ -6401,12 +6516,12 @@
         <v>15</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>11</v>
@@ -6415,12 +6530,12 @@
         <v>15</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>11</v>
@@ -6429,76 +6544,83 @@
         <v>15</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="29">
+      <c r="B28" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B6:E6"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="27.5"/>
-    <col customWidth="1" min="4" max="4" width="28.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28.38"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>208</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -6506,36 +6628,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
-        <v>2015.0</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5" s="4" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
-    </row>
-    <row r="7">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
@@ -6552,51 +6677,51 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="12"/>
+      <c r="C9" s="8"/>
       <c r="D9" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-    </row>
-    <row r="11">
+        <v>79</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-    </row>
-    <row r="12">
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-    </row>
-    <row r="13">
+        <v>79</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>14</v>
@@ -6605,12 +6730,12 @@
         <v>15</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>14</v>
@@ -6619,104 +6744,104 @@
         <v>15</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" s="12"/>
+        <v>66</v>
+      </c>
+      <c r="C15" s="8"/>
       <c r="D15" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+    </row>
+    <row r="18" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="s">
+      <c r="B18" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="12"/>
+      <c r="C18" s="8"/>
       <c r="D18" s="9" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="9" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="9"/>
     </row>
-    <row r="23">
+    <row r="23" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>11</v>
@@ -6725,12 +6850,12 @@
         <v>15</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>11</v>
@@ -6739,87 +6864,97 @@
         <v>15</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="14" t="s">
-        <v>196</v>
+      <c r="B28" s="12" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B6:E6"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
-        <v>2015.0</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5" s="4" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="B6" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
@@ -6836,76 +6971,86 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="B16" s="20"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" s="15"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="21" t="s">
-        <v>196</v>
+      <c r="B17" s="16" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B6:E6"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.47"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>221</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -6913,38 +7058,41 @@
         <v>222</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
-        <v>2019.0</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5" s="4" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
@@ -6961,14 +7109,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>20</v>
@@ -6977,36 +7125,36 @@
         <v>224</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>225</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>11</v>
@@ -7015,9 +7163,9 @@
         <v>229</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>11</v>
@@ -7026,69 +7174,76 @@
         <v>230</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="s">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="B18" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>228</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>197</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B6:E6"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>221</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -7096,38 +7251,41 @@
         <v>222</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
-        <v>2015.0</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5" s="4" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
@@ -7144,14 +7302,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>20</v>
@@ -7160,45 +7318,51 @@
         <v>224</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>225</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="s">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>196</v>
+      <c r="B15" s="12" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B6:E6"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>